--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_AOC.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR_AOC.xlsx
@@ -381,641 +381,641 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.3469874014721376</v>
+        <v>0.1656364582696275</v>
       </c>
       <c r="C2">
-        <v>0.5525039239127389</v>
+        <v>0.1140333333333333</v>
       </c>
       <c r="D2">
-        <v>0.9392834222375636</v>
+        <v>0.4352165078819998</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.3458299158779756</v>
+        <v>0.1057065498993653</v>
       </c>
       <c r="C3">
-        <v>0.3841201983251783</v>
+        <v>0.1102770921035048</v>
       </c>
       <c r="D3">
-        <v>0.729243993803292</v>
+        <v>0.2745574901519859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.2391153355282372</v>
+        <v>0.2217075139547674</v>
       </c>
       <c r="C4">
-        <v>0.2658729410936258</v>
+        <v>0.2973822371489913</v>
       </c>
       <c r="D4">
-        <v>0.5155182929568374</v>
+        <v>0.5432795026458455</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.1954232056758267</v>
+        <v>0.01425555555555558</v>
       </c>
       <c r="C5">
-        <v>0.1746922851579413</v>
+        <v>0.1084937034205995</v>
       </c>
       <c r="D5">
-        <v>0.4062587830798494</v>
+        <v>0.251972984712319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.2217075139547674</v>
+        <v>0.2504461066551363</v>
       </c>
       <c r="C6">
-        <v>0.2973822371489913</v>
+        <v>0.2546377795388034</v>
       </c>
       <c r="D6">
-        <v>0.5432795026458455</v>
+        <v>0.4520392883469307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.1057065498993653</v>
+        <v>0.001855555555555499</v>
       </c>
       <c r="C7">
-        <v>0.1102770921035048</v>
+        <v>0.06174538487865167</v>
       </c>
       <c r="D7">
-        <v>0.2745574901519859</v>
+        <v>0.2485331785159939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.02794599073523463</v>
+        <v>0.06164629552430523</v>
       </c>
       <c r="C8">
-        <v>0.07297610704060109</v>
+        <v>0.06093207949064294</v>
       </c>
       <c r="D8">
-        <v>0.208572632614522</v>
+        <v>0.1518430899805776</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.3439969809264296</v>
+        <v>0.006101722300085544</v>
       </c>
       <c r="C9">
-        <v>0.2674561685433386</v>
+        <v>0.1246299888957191</v>
       </c>
       <c r="D9">
-        <v>0.8290695673584256</v>
+        <v>0.2286558875452317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.09737837623630397</v>
+        <v>0.3064937430032676</v>
       </c>
       <c r="C10">
-        <v>0.1817619173760382</v>
+        <v>0.4949974742919987</v>
       </c>
       <c r="D10">
-        <v>0.3026413748776897</v>
+        <v>0.851964017508077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.001855555555555499</v>
+        <v>0.3469874014721376</v>
       </c>
       <c r="C11">
-        <v>0.06174538487865167</v>
+        <v>0.5525039239127389</v>
       </c>
       <c r="D11">
-        <v>0.2485331785159939</v>
+        <v>0.9392834222375636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.2504461066551363</v>
+        <v>0.1980632777852256</v>
       </c>
       <c r="C12">
-        <v>0.2546377795388034</v>
+        <v>0.3704080572413243</v>
       </c>
       <c r="D12">
-        <v>0.4520392883469307</v>
+        <v>0.6222519262006955</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1656364582696275</v>
+        <v>0.3135358815246574</v>
       </c>
       <c r="C13">
-        <v>0.1140333333333333</v>
+        <v>0.3166878206611351</v>
       </c>
       <c r="D13">
-        <v>0.4352165078819998</v>
+        <v>0.6312438683996313</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.01074444444444445</v>
+        <v>0.3439969809264296</v>
       </c>
       <c r="C14">
-        <v>0.539542381365083</v>
+        <v>0.2674561685433386</v>
       </c>
       <c r="D14">
-        <v>0.7742278185367445</v>
+        <v>0.8290695673584256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.001284879569573905</v>
+        <v>0.2158911291859935</v>
       </c>
       <c r="C15">
-        <v>0.2947587330579677</v>
+        <v>0.4402808625132648</v>
       </c>
       <c r="D15">
-        <v>0.3852380733356061</v>
+        <v>0.5778138548153773</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16">
-        <v>-0.02812222222222216</v>
+        <v>0.3671941047926067</v>
       </c>
       <c r="C16">
-        <v>0.4190419690631517</v>
+        <v>0.3932843623560955</v>
       </c>
       <c r="D16">
-        <v>0.5405720792125989</v>
+        <v>0.5743898880265543</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17">
-        <v>-0.004866666666666575</v>
+        <v>0.01154444444444447</v>
       </c>
       <c r="C17">
-        <v>0.09854012157289727</v>
+        <v>0.04969210402571422</v>
       </c>
       <c r="D17">
-        <v>0.4896919701185013</v>
+        <v>0.1696210315058644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.3064937430032676</v>
+        <v>0.3412049682915717</v>
       </c>
       <c r="C18">
-        <v>0.4949974742919987</v>
+        <v>0.4270443820966128</v>
       </c>
       <c r="D18">
-        <v>0.851964017508077</v>
+        <v>0.7267574161367297</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.4470997589084277</v>
+        <v>0.09737837623630397</v>
       </c>
       <c r="C19">
-        <v>0.5096788321468186</v>
+        <v>0.1817619173760382</v>
       </c>
       <c r="D19">
-        <v>1.154451724673331</v>
+        <v>0.3026413748776897</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.4278799224458372</v>
+        <v>0.2391153355282372</v>
       </c>
       <c r="C20">
-        <v>0.4853153065660065</v>
+        <v>0.2658729410936258</v>
       </c>
       <c r="D20">
-        <v>0.7870731304453064</v>
+        <v>0.5155182929568374</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.5496325541236597</v>
+        <v>-0.004866666666666575</v>
       </c>
       <c r="C21">
-        <v>0.6252659855784872</v>
+        <v>0.09854012157289727</v>
       </c>
       <c r="D21">
-        <v>1.138385209432712</v>
+        <v>0.4896919701185013</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.1980632777852256</v>
+        <v>0.0770057039873705</v>
       </c>
       <c r="C22">
-        <v>0.3704080572413243</v>
+        <v>0.08632748512688992</v>
       </c>
       <c r="D22">
-        <v>0.6222519262006955</v>
+        <v>0.2649250082381258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.06164629552430523</v>
+        <v>0.03601700091837634</v>
       </c>
       <c r="C23">
-        <v>0.06093207949064294</v>
+        <v>0.04434226267232699</v>
       </c>
       <c r="D23">
-        <v>0.1518430899805776</v>
+        <v>0.1260327767945706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.05292396085267559</v>
+        <v>0.1954232056758267</v>
       </c>
       <c r="C24">
-        <v>0.3608192607129737</v>
+        <v>0.1746922851579413</v>
       </c>
       <c r="D24">
-        <v>0.4898772093026026</v>
+        <v>0.4062587830798494</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.4742027028395286</v>
+        <v>0.2784908759301181</v>
       </c>
       <c r="C25">
-        <v>0.5332010803967087</v>
+        <v>0.3738051665953629</v>
       </c>
       <c r="D25">
-        <v>0.7003893237890435</v>
+        <v>0.7035737542057998</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.2784908759301181</v>
+        <v>0.001284879569573905</v>
       </c>
       <c r="C26">
-        <v>0.3738051665953629</v>
+        <v>0.2947587330579677</v>
       </c>
       <c r="D26">
-        <v>0.7035737542057998</v>
+        <v>0.3852380733356061</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.2985479722103835</v>
+        <v>0.4931966014855965</v>
       </c>
       <c r="C27">
-        <v>0.5170788953384786</v>
+        <v>0.6851576695350541</v>
       </c>
       <c r="D27">
-        <v>0.8217677789016034</v>
+        <v>1.059726210745495</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.0770057039873705</v>
+        <v>0.02794599073523463</v>
       </c>
       <c r="C28">
-        <v>0.08632748512688992</v>
+        <v>0.07297610704060109</v>
       </c>
       <c r="D28">
-        <v>0.2649250082381258</v>
+        <v>0.208572632614522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.03601700091837634</v>
+        <v>0.49382250681301</v>
       </c>
       <c r="C29">
-        <v>0.04434226267232699</v>
+        <v>0.4546840138326768</v>
       </c>
       <c r="D29">
-        <v>0.1260327767945706</v>
+        <v>0.8692129096285596</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.3135358815246574</v>
+        <v>0.4470997589084277</v>
       </c>
       <c r="C30">
-        <v>0.3166878206611351</v>
+        <v>0.5096788321468186</v>
       </c>
       <c r="D30">
-        <v>0.6312438683996313</v>
+        <v>1.154451724673331</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.3671941047926067</v>
+        <v>0.01074444444444445</v>
       </c>
       <c r="C31">
-        <v>0.3932843623560955</v>
+        <v>0.539542381365083</v>
       </c>
       <c r="D31">
-        <v>0.5743898880265543</v>
+        <v>0.7742278185367445</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.4931966014855965</v>
+        <v>0.5496325541236597</v>
       </c>
       <c r="C32">
-        <v>0.6851576695350541</v>
+        <v>0.6252659855784872</v>
       </c>
       <c r="D32">
-        <v>1.059726210745495</v>
+        <v>1.138385209432712</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.3190180926685514</v>
+        <v>0.3458299158779756</v>
       </c>
       <c r="C33">
-        <v>0.3796207669521876</v>
+        <v>0.3841201983251783</v>
       </c>
       <c r="D33">
-        <v>0.6135070584731168</v>
+        <v>0.729243993803292</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.49382250681301</v>
+        <v>0.3190180926685514</v>
       </c>
       <c r="C34">
-        <v>0.4546840138326768</v>
+        <v>0.3796207669521876</v>
       </c>
       <c r="D34">
-        <v>0.8692129096285596</v>
+        <v>0.6135070584731168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.01154444444444447</v>
+        <v>-0.02812222222222216</v>
       </c>
       <c r="C35">
-        <v>0.04969210402571422</v>
+        <v>0.4190419690631517</v>
       </c>
       <c r="D35">
-        <v>0.1696210315058644</v>
+        <v>0.5405720792125989</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.287282235700941</v>
+        <v>0.1140446856946893</v>
       </c>
       <c r="C36">
-        <v>0.3707691696848538</v>
+        <v>0.164179398232138</v>
       </c>
       <c r="D36">
-        <v>0.6076605796082912</v>
+        <v>0.4216641319447846</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.1140446856946893</v>
+        <v>0.05292396085267559</v>
       </c>
       <c r="C37">
-        <v>0.164179398232138</v>
+        <v>0.3608192607129737</v>
       </c>
       <c r="D37">
-        <v>0.4216641319447846</v>
+        <v>0.4898772093026026</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.2158911291859935</v>
+        <v>0.287282235700941</v>
       </c>
       <c r="C38">
-        <v>0.4402808625132648</v>
+        <v>0.3707691696848538</v>
       </c>
       <c r="D38">
-        <v>0.5778138548153773</v>
+        <v>0.6076605796082912</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.01425555555555558</v>
+        <v>0.4278799224458372</v>
       </c>
       <c r="C39">
-        <v>0.1084937034205995</v>
+        <v>0.4853153065660065</v>
       </c>
       <c r="D39">
-        <v>0.251972984712319</v>
+        <v>0.7870731304453064</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.3412049682915717</v>
+        <v>0.4742027028395286</v>
       </c>
       <c r="C40">
-        <v>0.4270443820966128</v>
+        <v>0.5332010803967087</v>
       </c>
       <c r="D40">
-        <v>0.7267574161367297</v>
+        <v>0.7003893237890435</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.006101722300085544</v>
+        <v>0.2985479722103835</v>
       </c>
       <c r="C41">
-        <v>0.1246299888957191</v>
+        <v>0.5170788953384786</v>
       </c>
       <c r="D41">
-        <v>0.2286558875452317</v>
+        <v>0.8217677789016034</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1043,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1055,7 +1055,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1331,7 +1331,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1391,7 +1391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1463,7 +1463,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1475,7 +1475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
